--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121511053</v>
       </c>
       <c r="B2" t="n">
-        <v>90096</v>
+        <v>90102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511499</v>
+        <v>121511136</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R3" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511136</v>
+        <v>121511499</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R4" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511053</v>
+        <v>121511136</v>
       </c>
       <c r="B2" t="n">
-        <v>90102</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511136</v>
+        <v>121511499</v>
       </c>
       <c r="B3" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R3" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511499</v>
+        <v>121511053</v>
       </c>
       <c r="B4" t="n">
-        <v>79226</v>
+        <v>90103</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R4" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511136</v>
+        <v>121511499</v>
       </c>
       <c r="B2" t="n">
         <v>79227</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R2" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511499</v>
+        <v>121511136</v>
       </c>
       <c r="B3" t="n">
         <v>79227</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R3" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511499</v>
+        <v>121511136</v>
       </c>
       <c r="B2" t="n">
         <v>79227</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R2" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511136</v>
+        <v>121511053</v>
       </c>
       <c r="B3" t="n">
-        <v>79227</v>
+        <v>90103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,31 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511053</v>
+        <v>121511499</v>
       </c>
       <c r="B4" t="n">
-        <v>90103</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R4" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121511136</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121511053</v>
       </c>
       <c r="B3" t="n">
-        <v>90103</v>
+        <v>90110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121511499</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511053</v>
+        <v>121511499</v>
       </c>
       <c r="B2" t="n">
-        <v>90110</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R2" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511499</v>
+        <v>121511136</v>
       </c>
       <c r="B3" t="n">
         <v>79234</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R3" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511136</v>
+        <v>121511053</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>90110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,31 +891,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511499</v>
+        <v>121511053</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>90110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R2" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511136</v>
+        <v>121511499</v>
       </c>
       <c r="B3" t="n">
         <v>79234</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R3" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511053</v>
+        <v>121511136</v>
       </c>
       <c r="B4" t="n">
-        <v>90110</v>
+        <v>79234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,31 +891,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511053</v>
+        <v>121511136</v>
       </c>
       <c r="B2" t="n">
-        <v>90110</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121511136</v>
+        <v>121511053</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>90110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,31 +891,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 48150-2024 artfynd.xlsx
+++ b/artfynd/A 48150-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121511136</v>
+        <v>121511499</v>
       </c>
       <c r="B2" t="n">
         <v>79234</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577097</v>
+        <v>577084</v>
       </c>
       <c r="R2" t="n">
-        <v>6517642</v>
+        <v>6517561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121511499</v>
+        <v>121511136</v>
       </c>
       <c r="B3" t="n">
         <v>79234</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577084</v>
+        <v>577097</v>
       </c>
       <c r="R3" t="n">
-        <v>6517561</v>
+        <v>6517642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
